--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486996_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486996_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.121</v>
+        <v>1.8734</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9216</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8005</v>
+        <v>-1.1266</v>
       </c>
       <c r="G2" t="n">
         <v>3.7164</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9673</v>
+        <v>0.7196</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9016</v>
+        <v>0.9801</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2604</v>
       </c>
       <c r="V2" t="n">
         <v>-2.3573</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ENABULELE OGUNSUYI</t>
+          <t>H. SALOMON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4997</v>
+        <v>0.2319</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1132</v>
+        <v>1.1958</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6129</v>
+        <v>-0.9639</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.016</v>
+        <v>1.2584</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7427</v>
+        <v>-0.1624</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2733</v>
+        <v>1.4208</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0931</v>
+        <v>1.1765</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0253</v>
+        <v>0.0584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>1.1181</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1091</v>
+        <v>0.0819</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7174</v>
+        <v>-0.2208</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3917</v>
+        <v>0.3027</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2321</v>
+        <v>0.4107</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8504</v>
+        <v>-0.2586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3871</v>
+        <v>0.0193</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4632</v>
+        <v>-0.2779</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5668</v>
+        <v>-1.1786</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.5668</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. SALOMON</t>
+          <t>M. ENABULELE OGUNSUYI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0663</v>
+        <v>-0.6805</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9866</v>
+        <v>-1.582</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0529</v>
+        <v>0.9015</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2584</v>
+        <v>-2.016</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1624</v>
+        <v>-0.7427</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4208</v>
+        <v>-1.2733</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1765</v>
+        <v>0.0931</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0584</v>
+        <v>-0.0253</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1181</v>
+        <v>0.1184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0819</v>
+        <v>-2.1091</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2208</v>
+        <v>-0.7174</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3027</v>
+        <v>-1.3917</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4107</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5567</v>
+        <v>0.6702</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1899</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3669</v>
+        <v>0.7518</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1786</v>
+        <v>-0.5668</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.5668</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1742</v>
+        <v>-1.1429</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.836</v>
+        <v>-0.6268</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3382</v>
+        <v>-0.516</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4699</v>
@@ -844,13 +844,13 @@
         <v>0.4107</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0636</v>
+        <v>0.0949</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1976</v>
+        <v>0.0116</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2612</v>
+        <v>0.0834</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1786</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5424</v>
+        <v>-2.4682</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1141</v>
+        <v>-2.7731</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5717</v>
+        <v>0.3049</v>
       </c>
       <c r="G6" t="n">
         <v>-1.7912</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5458</v>
+        <v>-0.4717</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6587</v>
+        <v>-0.3178</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1129</v>
+        <v>-0.1539</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8233</v>
+        <v>-2.5821</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6484</v>
+        <v>-1.5554</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.175</v>
+        <v>-1.0268</v>
       </c>
       <c r="G7" t="n">
         <v>-4.6051</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0602</v>
+        <v>0.181</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3562</v>
+        <v>0.4492</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4164</v>
+        <v>-0.2682</v>
       </c>
       <c r="V7" t="n">
         <v>1.6366</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3317</v>
+        <v>-3.172</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9619</v>
+        <v>-2.0394</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3698</v>
+        <v>-1.1327</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9708</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6751</v>
+        <v>-0.5154</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0468</v>
+        <v>-0.1242</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6283</v>
+        <v>-0.3912</v>
       </c>
       <c r="V8" t="n">
         <v>-0.4805</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2884</v>
+        <v>-3.5308</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.263</v>
+        <v>-4.7129</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9746</v>
+        <v>1.1821</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1749</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0047</v>
+        <v>-0.247</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0462</v>
+        <v>-0.4961</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0416</v>
+        <v>0.249</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6982</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1409</v>
+        <v>-4.5175</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5403</v>
+        <v>-4.0947</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6007</v>
+        <v>-0.4228</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9343</v>
@@ -1234,13 +1234,13 @@
         <v>1.6427</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.1725</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.283</v>
+        <v>0.1626</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5129</v>
+        <v>-0.3351</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.6263</v>
+        <v>-6.573</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.6196</v>
+        <v>-7.8331</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9933999999999999</v>
+        <v>1.2601</v>
       </c>
       <c r="G11" t="n">
         <v>-6.7843</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4108</v>
+        <v>-0.3575</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0076</v>
+        <v>-0.2211</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4032</v>
+        <v>-0.1364</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4579</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.0313</v>
+        <v>-7.1956</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5718</v>
+        <v>-3.0918</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4595</v>
+        <v>-4.1038</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2643</v>
@@ -1390,13 +1390,13 @@
         <v>2.2588</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6417</v>
+        <v>-0.806</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9026</v>
+        <v>-0.4226</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7392</v>
+        <v>-0.3834</v>
       </c>
       <c r="V12" t="n">
         <v>-2.3573</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-31.4041</v>
+        <v>-29.7573</v>
       </c>
       <c r="E13" t="n">
-        <v>-25.7601</v>
+        <v>-24.1134</v>
       </c>
       <c r="F13" t="n">
         <v>-5.644</v>
@@ -1459,7 +1459,7 @@
         <v>-5.445</v>
       </c>
       <c r="P13" t="n">
-        <v>3.080299999999999</v>
+        <v>3.0803</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.3204</v>
@@ -1468,13 +1468,13 @@
         <v>15.4008</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.8096</v>
+        <v>-1.163</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6875</v>
+        <v>-0.04059999999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1224</v>
+        <v>-1.1223</v>
       </c>
       <c r="V13" t="n">
         <v>-7.6386</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1947</v>
+        <v>7.504</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9004</v>
+        <v>3.8418</v>
       </c>
       <c r="F14" t="n">
-        <v>3.2943</v>
+        <v>3.6622</v>
       </c>
       <c r="G14" t="n">
         <v>7.8323</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6108</v>
+        <v>0.6985</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7827</v>
+        <v>0.1587</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1719</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.9849</v>
+        <v>5.6989</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2594</v>
+        <v>4.0502</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7255</v>
+        <v>1.6487</v>
       </c>
       <c r="G15" t="n">
         <v>4.1499</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8904</v>
+        <v>0.6044</v>
       </c>
       <c r="T15" t="n">
-        <v>0.209</v>
+        <v>-0.0002</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6814</v>
+        <v>0.6046</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6982</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3647</v>
+        <v>5.6125</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8451</v>
+        <v>1.931</v>
       </c>
       <c r="F16" t="n">
-        <v>4.5196</v>
+        <v>3.6815</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8001</v>
+        <v>3.7219</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>4.5745</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6001</v>
+        <v>-0.8525</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4071</v>
+        <v>2.0001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2492</v>
+        <v>4.0397</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1579</v>
+        <v>-2.0396</v>
       </c>
       <c r="M16" t="n">
-        <v>1.393</v>
+        <v>1.7218</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0492</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4422</v>
+        <v>1.187</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.4374</v>
+        <v>-1.2321</v>
       </c>
       <c r="R16" t="n">
         <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6611</v>
+        <v>0.3013</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8754999999999999</v>
+        <v>-0.0156</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7857</v>
+        <v>0.317</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6982</v>
+        <v>1.1786</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1157</v>
+        <v>4.561</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7218</v>
+        <v>0.4267</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3938</v>
+        <v>4.1342</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7219</v>
+        <v>2.8001</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5745</v>
+        <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8525</v>
+        <v>1.6001</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0001</v>
+        <v>1.4071</v>
       </c>
       <c r="K17" t="n">
-        <v>4.0397</v>
+        <v>1.2492</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0396</v>
+        <v>0.1579</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7218</v>
+        <v>1.393</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5348000000000001</v>
+        <v>-0.0492</v>
       </c>
       <c r="O17" t="n">
-        <v>1.187</v>
+        <v>1.4422</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2321</v>
+        <v>-1.4374</v>
       </c>
       <c r="R17" t="n">
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1956</v>
+        <v>0.8573</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2249</v>
+        <v>0.457</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0293</v>
+        <v>0.4003</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1786</v>
+        <v>0.6982</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.5285</v>
+        <v>3.5784</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2544</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>4.2741</v>
+        <v>4.2654</v>
       </c>
       <c r="G18" t="n">
         <v>0.3518</v>
@@ -1858,13 +1858,13 @@
         <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>0.3498</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5728</v>
+        <v>0.6314</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2729</v>
+        <v>-0.2816</v>
       </c>
       <c r="V18" t="n">
         <v>2.4661</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7088</v>
+        <v>3.2024</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6616</v>
+        <v>0.304</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0471</v>
+        <v>2.8984</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8784</v>
+        <v>1.2781</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0056</v>
+        <v>1.7126</v>
       </c>
       <c r="I19" t="n">
-        <v>1.884</v>
+        <v>-0.4345</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2386</v>
+        <v>0.2483</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0638</v>
+        <v>1.9855</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3024</v>
+        <v>-1.7372</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6398</v>
+        <v>1.0298</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0582</v>
+        <v>-0.2729</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5816</v>
+        <v>1.3027</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.616</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R19" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3294</v>
+        <v>0.5938</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2362</v>
+        <v>-0.2481</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0931</v>
+        <v>0.8419</v>
       </c>
       <c r="V19" t="n">
-        <v>2.117</v>
+        <v>2.3573</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4189</v>
+        <v>2.3573</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0585</v>
+        <v>2.5344</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6852</v>
+        <v>0.3478</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7437</v>
+        <v>2.1866</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5246</v>
+        <v>0.8784</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0193</v>
+        <v>-1.0056</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5054</v>
+        <v>1.884</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1952</v>
+        <v>0.2386</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1557</v>
+        <v>-1.0638</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0395</v>
+        <v>1.3024</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3294</v>
+        <v>0.6398</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1365</v>
+        <v>0.0582</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4659</v>
+        <v>0.5816</v>
       </c>
       <c r="P20" t="n">
         <v>-0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-1.2321</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4517</v>
+        <v>0.155</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6042</v>
+        <v>-0.0776</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8475</v>
+        <v>0.2326</v>
       </c>
       <c r="V20" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.4189</v>
+      </c>
+      <c r="X20" t="n">
         <v>0.6982</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-0.4579</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.1561</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0046</v>
+        <v>1.586</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4282</v>
+        <v>-1.2082</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4329</v>
+        <v>2.7942</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2781</v>
+        <v>0.5246</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7126</v>
+        <v>0.0193</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4345</v>
+        <v>0.5054</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2483</v>
+        <v>0.1952</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9855</v>
+        <v>0.1557</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7372</v>
+        <v>0.0395</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0298</v>
+        <v>0.3294</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2729</v>
+        <v>-0.1365</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3027</v>
+        <v>0.4659</v>
       </c>
       <c r="P21" t="n">
+        <v>-0.616</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.0534</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.604</v>
+        <v>0.9792</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9804</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3764</v>
+        <v>0.898</v>
       </c>
       <c r="V21" t="n">
-        <v>2.3573</v>
+        <v>0.6982</v>
       </c>
       <c r="W21" t="n">
-        <v>2.3573</v>
+        <v>-0.4579</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.1561</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3486</v>
+        <v>0.4079</v>
       </c>
       <c r="E22" t="n">
         <v>0.0195</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3291</v>
+        <v>0.3884</v>
       </c>
       <c r="G22" t="n">
         <v>0.2432</v>
@@ -2170,13 +2170,13 @@
         <v>0.2053</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3486</v>
+        <v>0.4079</v>
       </c>
       <c r="E23" t="n">
         <v>0.0195</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3291</v>
+        <v>0.3884</v>
       </c>
       <c r="G23" t="n">
         <v>0.2432</v>
@@ -2248,13 +2248,13 @@
         <v>0.2053</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5221</v>
+        <v>0.3776</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2826</v>
+        <v>-1.7596</v>
       </c>
       <c r="F24" t="n">
-        <v>1.7605</v>
+        <v>2.1371</v>
       </c>
       <c r="G24" t="n">
         <v>1.7692</v>
@@ -2326,13 +2326,13 @@
         <v>1.4374</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1126</v>
+        <v>-0.213</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3875</v>
+        <v>0.1355</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7251</v>
+        <v>-0.3485</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1786</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7315</v>
+        <v>-2.6722</v>
       </c>
       <c r="E25" t="n">
         <v>-3.0607</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3291</v>
+        <v>0.3884</v>
       </c>
       <c r="G25" t="n">
         <v>0.2432</v>
@@ -2404,13 +2404,13 @@
         <v>0.2053</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>31.40399999999999</v>
+        <v>32.7988</v>
       </c>
       <c r="E26" t="n">
-        <v>4.225000000000001</v>
+        <v>4.225000000000003</v>
       </c>
       <c r="F26" t="n">
-        <v>27.1788</v>
+        <v>28.5735</v>
       </c>
       <c r="G26" t="n">
-        <v>24.0359</v>
+        <v>24.03590000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>7.655899999999999</v>
+        <v>7.6559</v>
       </c>
       <c r="I26" t="n">
         <v>16.3801</v>
@@ -2482,13 +2482,13 @@
         <v>12.3204</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8099</v>
+        <v>4.204199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.1222</v>
+        <v>1.1223</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6876</v>
+        <v>3.081999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>7.638599999999999</v>
